--- a/artfynd/A 23163-2025 artfynd.xlsx
+++ b/artfynd/A 23163-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -913,6 +913,103 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129780200</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Grishol, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>471633</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6779614</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 23163-2025 artfynd.xlsx
+++ b/artfynd/A 23163-2025 artfynd.xlsx
@@ -918,7 +918,7 @@
         <v>129780200</v>
       </c>
       <c r="B4" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 23163-2025 artfynd.xlsx
+++ b/artfynd/A 23163-2025 artfynd.xlsx
@@ -918,7 +918,7 @@
         <v>129780200</v>
       </c>
       <c r="B4" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 23163-2025 artfynd.xlsx
+++ b/artfynd/A 23163-2025 artfynd.xlsx
@@ -918,7 +918,7 @@
         <v>129780200</v>
       </c>
       <c r="B4" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 23163-2025 artfynd.xlsx
+++ b/artfynd/A 23163-2025 artfynd.xlsx
@@ -918,7 +918,7 @@
         <v>129780200</v>
       </c>
       <c r="B4" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 23163-2025 artfynd.xlsx
+++ b/artfynd/A 23163-2025 artfynd.xlsx
@@ -675,61 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124170639</v>
+        <v>129780200</v>
       </c>
       <c r="B2" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Våmhus, Våmhus, Dlr</t>
+          <t>Grishol, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>471630</v>
+        <v>471633</v>
       </c>
       <c r="R2" t="n">
-        <v>6779589</v>
+        <v>6779614</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>13:03</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>13:03</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,49 +760,44 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Petter Westberg</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Petter Westberg</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124170640</v>
+        <v>124170639</v>
       </c>
       <c r="B3" t="n">
-        <v>57666</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -915,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129780200</v>
+        <v>124170640</v>
       </c>
       <c r="B4" t="n">
-        <v>79095</v>
+        <v>58114</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -926,37 +898,45 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Grishol, Dlr</t>
+          <t>Våmhus, Våmhus, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471633</v>
+        <v>471630</v>
       </c>
       <c r="R4" t="n">
-        <v>6779614</v>
+        <v>6779589</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -980,12 +960,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-04-17</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-04-17</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1000,12 +990,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Petter Westberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Petter Westberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 23163-2025 artfynd.xlsx
+++ b/artfynd/A 23163-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129780200</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124170639</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -999,8 +1014,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124170640</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>